--- a/dados/administrativos.xlsx
+++ b/dados/administrativos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{860EC8B7-8E04-45FA-8184-7B115C4CA23A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9100050F-5651-43D4-98B8-846A198D251E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="57">
   <si>
     <t>Id</t>
   </si>
@@ -186,6 +186,27 @@
   </si>
   <si>
     <t>Melhorias na segurança interna da instituição.</t>
+  </si>
+  <si>
+    <t>Atividades voltadas ao meio ambiente sinto que falta.</t>
+  </si>
+  <si>
+    <t>Sem sugestão</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aviso prévio dos eventos para melhor organização pessoal. </t>
+  </si>
+  <si>
+    <t>Por enquanto, estou satisfeita com as mudanças que foram realizadas por meio de outras avaliações e não tenho do que reclamar no momento.  Entendo que questões salariais dependem de decisões superiores e de diversos fatores internos. No entanto, acredito que poderia haver uma análise mais detalhada dos setores e das funções exercidas por cada colaborador, considerando que alguns funcionários desempenham atividades além das atribuições do cargo em que estão registrados.  Também considero importante que a instituição valorize o crescimento e o desenvolvimento profissional dos colaboradores, reconhecendo adequadamente aqueles que assumem maiores responsabilidades no dia a dia.</t>
+  </si>
+  <si>
+    <t>É necessário maior participação nos eventos promovidos, vejo que são feitos muitos, mas não tem tanta adesão dos colaboradores.</t>
+  </si>
+  <si>
+    <t>A limpeza dos banheiros está insuficiente, melhor nesse aspecto contratar mais funcionário. Voltar com o aniversariantes do mês</t>
+  </si>
+  <si>
+    <t>Só tenho elogios. Ambiente de trabalho super tranquilo, ao lado de pessoas maravilhosas!</t>
   </si>
 </sst>
 </file>
@@ -221,10 +242,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -274,8 +297,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:L34" totalsRowShown="0">
-  <autoFilter ref="A1:L34" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:L44" totalsRowShown="0">
+  <autoFilter ref="A1:L44" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="9">
       <extLst>
@@ -365,7 +388,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="rt8JIBHfx0mATf2o1c2YZSr5bAZAsa1Hi1pL7TTHnqJUNzZHRkpMSUdPQTlTUEo3NEJCVk1XVTJGQy4u" isFormConnected="1" maxResponseId="33" latestEventMarker="0">
+      <xlmsforms:msForm id="rt8JIBHfx0mATf2o1c2YZSr5bAZAsa1Hi1pL7TTHnqJUNzZHRkpMSUdPQTlTUEo3NEJCVk1XVTJGQy4u" isFormConnected="1" maxResponseId="43" latestEventMarker="10">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -681,7 +704,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="12" width="20" bestFit="1" customWidth="1"/>
@@ -1880,6 +1903,366 @@
         <v>49</v>
       </c>
     </row>
+    <row r="35" spans="1:12">
+      <c r="A35" s="3">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2">
+        <v>46156.763680555603</v>
+      </c>
+      <c r="C35" s="2">
+        <v>46156.764606481498</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K35" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L35" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
+      <c r="A36" s="3">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2">
+        <v>46156.765520833302</v>
+      </c>
+      <c r="C36" s="2">
+        <v>46156.766319444403</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K36" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L36" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="A37" s="3">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2">
+        <v>46156.767314814802</v>
+      </c>
+      <c r="C37" s="2">
+        <v>46156.769629629598</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K37" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L37" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12">
+      <c r="A38" s="3">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2">
+        <v>46156.773182870398</v>
+      </c>
+      <c r="C38" s="2">
+        <v>46156.776215277801</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J38" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K38" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="L38" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
+      <c r="A39" s="3">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2">
+        <v>46156.832916666703</v>
+      </c>
+      <c r="C39" s="2">
+        <v>46156.833888888897</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J39" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K39" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L39" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
+      <c r="A40" s="3">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2">
+        <v>46157.330590277801</v>
+      </c>
+      <c r="C40" s="2">
+        <v>46157.332777777803</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J40" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K40" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L40" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
+      <c r="A41" s="3">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2">
+        <v>46157.465949074103</v>
+      </c>
+      <c r="C41" s="2">
+        <v>46157.4682060185</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J41" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K41" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="L41" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
+      <c r="A42" s="3">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2">
+        <v>46157.482106481497</v>
+      </c>
+      <c r="C42" s="2">
+        <v>46157.483981481499</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J42" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K42" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="L42" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
+      <c r="A43" s="3">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2">
+        <v>46157.483680555597</v>
+      </c>
+      <c r="C43" s="2">
+        <v>46157.487662036998</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J43" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K43" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L43" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12">
+      <c r="A44" s="3">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2">
+        <v>46157.6006597222</v>
+      </c>
+      <c r="C44" s="2">
+        <v>46157.601377314801</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J44" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K44" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L44" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/dados/administrativos.xlsx
+++ b/dados/administrativos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9100050F-5651-43D4-98B8-846A198D251E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D0A0CC25-811D-4AA1-A936-E92DF5B1D081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -242,11 +242,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1904,7 +1903,7 @@
       </c>
     </row>
     <row r="35" spans="1:12">
-      <c r="A35" s="3">
+      <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" s="2">
@@ -1913,34 +1912,34 @@
       <c r="C35" s="2">
         <v>46156.764606481498</v>
       </c>
-      <c r="D35" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4" t="s">
+      <c r="D35" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G35" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I35" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J35" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K35" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L35" s="4" t="s">
+      <c r="G35" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L35" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="36" spans="1:12">
-      <c r="A36" s="3">
+      <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" s="2">
@@ -1949,34 +1948,34 @@
       <c r="C36" s="2">
         <v>46156.766319444403</v>
       </c>
-      <c r="D36" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H36" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I36" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J36" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K36" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L36" s="4" t="s">
+      <c r="D36" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L36" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="37" spans="1:12">
-      <c r="A37" s="3">
+      <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" s="2">
@@ -1985,34 +1984,34 @@
       <c r="C37" s="2">
         <v>46156.769629629598</v>
       </c>
-      <c r="D37" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4" t="s">
+      <c r="D37" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G37" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H37" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I37" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J37" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K37" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L37" s="4" t="s">
+      <c r="G37" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L37" s="3" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="38" spans="1:12">
-      <c r="A38" s="3">
+      <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" s="2">
@@ -2021,34 +2020,34 @@
       <c r="C38" s="2">
         <v>46156.776215277801</v>
       </c>
-      <c r="D38" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H38" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I38" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="J38" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K38" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="L38" s="4" t="s">
+      <c r="D38" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L38" s="3" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="39" spans="1:12">
-      <c r="A39" s="3">
+      <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" s="2">
@@ -2057,34 +2056,34 @@
       <c r="C39" s="2">
         <v>46156.833888888897</v>
       </c>
-      <c r="D39" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H39" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I39" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J39" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K39" s="4" t="s">
+      <c r="D39" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K39" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L39" s="4" t="s">
+      <c r="L39" s="3" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="40" spans="1:12">
-      <c r="A40" s="3">
+      <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" s="2">
@@ -2093,34 +2092,34 @@
       <c r="C40" s="2">
         <v>46157.332777777803</v>
       </c>
-      <c r="D40" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4" t="s">
+      <c r="D40" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G40" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H40" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I40" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J40" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K40" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L40" s="4" t="s">
+      <c r="G40" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L40" s="3" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="3">
+      <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" s="2">
@@ -2129,34 +2128,34 @@
       <c r="C41" s="2">
         <v>46157.4682060185</v>
       </c>
-      <c r="D41" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4" t="s">
+      <c r="D41" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G41" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H41" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I41" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J41" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K41" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="L41" s="4" t="s">
+      <c r="G41" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L41" s="3" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="42" spans="1:12">
-      <c r="A42" s="3">
+      <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" s="2">
@@ -2165,34 +2164,34 @@
       <c r="C42" s="2">
         <v>46157.483981481499</v>
       </c>
-      <c r="D42" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4" t="s">
+      <c r="D42" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G42" s="4" t="s">
+      <c r="G42" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H42" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I42" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J42" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K42" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="L42" s="4" t="s">
+      <c r="H42" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L42" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="43" spans="1:12">
-      <c r="A43" s="3">
+      <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" s="2">
@@ -2201,34 +2200,34 @@
       <c r="C43" s="2">
         <v>46157.487662036998</v>
       </c>
-      <c r="D43" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4" t="s">
+      <c r="D43" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G43" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H43" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I43" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J43" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K43" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L43" s="4" t="s">
+      <c r="G43" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L43" s="3" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="44" spans="1:12">
-      <c r="A44" s="3">
+      <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" s="2">
@@ -2237,29 +2236,29 @@
       <c r="C44" s="2">
         <v>46157.601377314801</v>
       </c>
-      <c r="D44" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4" t="s">
+      <c r="D44" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G44" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H44" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I44" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J44" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K44" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L44" s="4" t="s">
+      <c r="G44" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L44" s="3" t="s">
         <v>51</v>
       </c>
     </row>

--- a/dados/administrativos.xlsx
+++ b/dados/administrativos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D0A0CC25-811D-4AA1-A936-E92DF5B1D081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F5B4F6E4-274C-4CCE-B108-210258843EFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="71">
   <si>
     <t>Id</t>
   </si>
@@ -207,6 +207,48 @@
   </si>
   <si>
     <t>Só tenho elogios. Ambiente de trabalho super tranquilo, ao lado de pessoas maravilhosas!</t>
+  </si>
+  <si>
+    <t>Não tenho nenhuma.</t>
+  </si>
+  <si>
+    <t>No momento, sem comentários.</t>
+  </si>
+  <si>
+    <t>Segurança: reforçar vigilância, iluminação e controle de acesso na instituição</t>
+  </si>
+  <si>
+    <t>Nada a declarar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acho que precisa divulgar mais os eventos para os colaboradores, muitas vezes tem eventos e nem ficam sabendo, só sabem quando o aluno vem pedir informações e saimos ligando nos setores para saber do que se trata. </t>
+  </si>
+  <si>
+    <t>Vejo que há uma necessidade de comunicação mais direta com os colaboradores para otimizar a participação nas pesquisas.</t>
+  </si>
+  <si>
+    <t>Retorno das missas no campos 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">melhorar o trabalho em equipe </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Educação </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atividades em conjunto com outras áreas como oficinas e projetos </t>
+  </si>
+  <si>
+    <t>Dar oportunidades para os colaboradores mudar de cargos, principalmente os colaboradores da limpeza que nunca tem oportunidades,.os colaboradores do administrativo que sempre mudam de cargos.as oportunidades que surgem  já tem o grupo escolhidos</t>
+  </si>
+  <si>
+    <t>Na minha opinião vejo que precisa ser melhorado algumas atividades.E minha sugestão e ter um RT -Responsavel Técnico nas areas experimentão que não seja professor que esteja no dia a dia organizador e direcionado as atividades e melhorado a organização das atividades do setor.</t>
+  </si>
+  <si>
+    <t>Gostaria de sugerir uma revisão em relação aos cargos e salários da equipe. Acredito que as responsabilidades exercidas no dia a dia vão além da função de auxiliar, sendo mais compatíveis com a função de assistente.  Também seria importante avaliar uma melhoria salarial, como forma de reconhecimento pelo comprometimento, pelas demandas realizadas e pela contribuição de cada colaborador para o bom funcionamento do setor.  Essa valorização certamente contribuirá ainda mais para a motivação e o desempenho da equipe.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No momento só parabenizar a instituição muito bom mesmo. </t>
   </si>
 </sst>
 </file>
@@ -242,11 +284,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -296,8 +337,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:L44" totalsRowShown="0">
-  <autoFilter ref="A1:L44" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:L58" totalsRowShown="0">
+  <autoFilter ref="A1:L58" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="9">
       <extLst>
@@ -387,7 +428,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="rt8JIBHfx0mATf2o1c2YZSr5bAZAsa1Hi1pL7TTHnqJUNzZHRkpMSUdPQTlTUEo3NEJCVk1XVTJGQy4u" isFormConnected="1" maxResponseId="43" latestEventMarker="10">
+      <xlmsforms:msForm id="rt8JIBHfx0mATf2o1c2YZSr5bAZAsa1Hi1pL7TTHnqJUNzZHRkpMSUdPQTlTUEo3NEJCVk1XVTJGQy4u" isFormConnected="1" maxResponseId="57" latestEventMarker="24">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -703,7 +744,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L58"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="12" width="20" bestFit="1" customWidth="1"/>
@@ -1907,34 +1948,33 @@
         <v>34</v>
       </c>
       <c r="B35" s="2">
-        <v>46156.763680555603</v>
+        <v>46156.763680555552</v>
       </c>
       <c r="C35" s="2">
-        <v>46156.764606481498</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="L35" s="3" t="s">
+        <v>46156.764606481483</v>
+      </c>
+      <c r="D35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" t="s">
+        <v>18</v>
+      </c>
+      <c r="G35" t="s">
+        <v>14</v>
+      </c>
+      <c r="H35" t="s">
+        <v>14</v>
+      </c>
+      <c r="I35" t="s">
+        <v>14</v>
+      </c>
+      <c r="J35" t="s">
+        <v>14</v>
+      </c>
+      <c r="K35" t="s">
+        <v>14</v>
+      </c>
+      <c r="L35" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1943,34 +1983,33 @@
         <v>35</v>
       </c>
       <c r="B36" s="2">
-        <v>46156.765520833302</v>
+        <v>46156.765520833331</v>
       </c>
       <c r="C36" s="2">
-        <v>46156.766319444403</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K36" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="L36" s="3" t="s">
+        <v>46156.766319444447</v>
+      </c>
+      <c r="D36" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" t="s">
+        <v>15</v>
+      </c>
+      <c r="G36" t="s">
+        <v>15</v>
+      </c>
+      <c r="H36" t="s">
+        <v>14</v>
+      </c>
+      <c r="I36" t="s">
+        <v>14</v>
+      </c>
+      <c r="J36" t="s">
+        <v>14</v>
+      </c>
+      <c r="K36" t="s">
+        <v>14</v>
+      </c>
+      <c r="L36" s="1" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1979,34 +2018,33 @@
         <v>36</v>
       </c>
       <c r="B37" s="2">
-        <v>46156.767314814802</v>
+        <v>46156.767314814817</v>
       </c>
       <c r="C37" s="2">
-        <v>46156.769629629598</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K37" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="L37" s="3" t="s">
+        <v>46156.769629629627</v>
+      </c>
+      <c r="D37" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37" t="s">
+        <v>14</v>
+      </c>
+      <c r="H37" t="s">
+        <v>14</v>
+      </c>
+      <c r="I37" t="s">
+        <v>15</v>
+      </c>
+      <c r="J37" t="s">
+        <v>14</v>
+      </c>
+      <c r="K37" t="s">
+        <v>14</v>
+      </c>
+      <c r="L37" t="s">
         <v>50</v>
       </c>
     </row>
@@ -2015,34 +2053,33 @@
         <v>37</v>
       </c>
       <c r="B38" s="2">
-        <v>46156.773182870398</v>
+        <v>46156.773182870369</v>
       </c>
       <c r="C38" s="2">
-        <v>46156.776215277801</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L38" s="3" t="s">
+        <v>46156.77621527778</v>
+      </c>
+      <c r="D38" t="s">
+        <v>12</v>
+      </c>
+      <c r="F38" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" t="s">
+        <v>13</v>
+      </c>
+      <c r="H38" t="s">
+        <v>14</v>
+      </c>
+      <c r="I38" t="s">
+        <v>13</v>
+      </c>
+      <c r="J38" t="s">
+        <v>13</v>
+      </c>
+      <c r="K38" t="s">
+        <v>13</v>
+      </c>
+      <c r="L38" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2051,34 +2088,33 @@
         <v>38</v>
       </c>
       <c r="B39" s="2">
-        <v>46156.832916666703</v>
+        <v>46156.832916666666</v>
       </c>
       <c r="C39" s="2">
-        <v>46156.833888888897</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="K39" s="3" t="s">
+        <v>46156.83388888889</v>
+      </c>
+      <c r="D39" t="s">
+        <v>12</v>
+      </c>
+      <c r="F39" t="s">
+        <v>15</v>
+      </c>
+      <c r="G39" t="s">
+        <v>15</v>
+      </c>
+      <c r="H39" t="s">
+        <v>14</v>
+      </c>
+      <c r="I39" t="s">
+        <v>15</v>
+      </c>
+      <c r="J39" t="s">
+        <v>15</v>
+      </c>
+      <c r="K39" t="s">
         <v>21</v>
       </c>
-      <c r="L39" s="3" t="s">
+      <c r="L39" t="s">
         <v>52</v>
       </c>
     </row>
@@ -2087,34 +2123,33 @@
         <v>39</v>
       </c>
       <c r="B40" s="2">
-        <v>46157.330590277801</v>
+        <v>46157.330590277779</v>
       </c>
       <c r="C40" s="2">
-        <v>46157.332777777803</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K40" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="L40" s="3" t="s">
+        <v>46157.332777777781</v>
+      </c>
+      <c r="D40" t="s">
+        <v>12</v>
+      </c>
+      <c r="F40" t="s">
+        <v>18</v>
+      </c>
+      <c r="G40" t="s">
+        <v>14</v>
+      </c>
+      <c r="H40" t="s">
+        <v>14</v>
+      </c>
+      <c r="I40" t="s">
+        <v>14</v>
+      </c>
+      <c r="J40" t="s">
+        <v>14</v>
+      </c>
+      <c r="K40" t="s">
+        <v>14</v>
+      </c>
+      <c r="L40" t="s">
         <v>53</v>
       </c>
     </row>
@@ -2123,34 +2158,33 @@
         <v>40</v>
       </c>
       <c r="B41" s="2">
-        <v>46157.465949074103</v>
+        <v>46157.465949074074</v>
       </c>
       <c r="C41" s="2">
-        <v>46157.4682060185</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L41" s="3" t="s">
+        <v>46157.468206018515</v>
+      </c>
+      <c r="D41" t="s">
+        <v>12</v>
+      </c>
+      <c r="F41" t="s">
+        <v>18</v>
+      </c>
+      <c r="G41" t="s">
+        <v>14</v>
+      </c>
+      <c r="H41" t="s">
+        <v>13</v>
+      </c>
+      <c r="I41" t="s">
+        <v>14</v>
+      </c>
+      <c r="J41" t="s">
+        <v>13</v>
+      </c>
+      <c r="K41" t="s">
+        <v>13</v>
+      </c>
+      <c r="L41" t="s">
         <v>54</v>
       </c>
     </row>
@@ -2159,34 +2193,33 @@
         <v>41</v>
       </c>
       <c r="B42" s="2">
-        <v>46157.482106481497</v>
+        <v>46157.482106481482</v>
       </c>
       <c r="C42" s="2">
-        <v>46157.483981481499</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3" t="s">
+        <v>46157.483981481484</v>
+      </c>
+      <c r="D42" t="s">
+        <v>12</v>
+      </c>
+      <c r="F42" t="s">
         <v>21</v>
       </c>
-      <c r="G42" s="3" t="s">
+      <c r="G42" t="s">
         <v>21</v>
       </c>
-      <c r="H42" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L42" s="3" t="s">
+      <c r="H42" t="s">
+        <v>15</v>
+      </c>
+      <c r="I42" t="s">
+        <v>15</v>
+      </c>
+      <c r="J42" t="s">
+        <v>15</v>
+      </c>
+      <c r="K42" t="s">
+        <v>15</v>
+      </c>
+      <c r="L42" t="s">
         <v>55</v>
       </c>
     </row>
@@ -2195,34 +2228,33 @@
         <v>42</v>
       </c>
       <c r="B43" s="2">
-        <v>46157.483680555597</v>
+        <v>46157.483680555553</v>
       </c>
       <c r="C43" s="2">
-        <v>46157.487662036998</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="L43" s="3" t="s">
+        <v>46157.487662037034</v>
+      </c>
+      <c r="D43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F43" t="s">
+        <v>18</v>
+      </c>
+      <c r="G43" t="s">
+        <v>14</v>
+      </c>
+      <c r="H43" t="s">
+        <v>14</v>
+      </c>
+      <c r="I43" t="s">
+        <v>14</v>
+      </c>
+      <c r="J43" t="s">
+        <v>14</v>
+      </c>
+      <c r="K43" t="s">
+        <v>14</v>
+      </c>
+      <c r="L43" t="s">
         <v>56</v>
       </c>
     </row>
@@ -2231,35 +2263,524 @@
         <v>43</v>
       </c>
       <c r="B44" s="2">
-        <v>46157.6006597222</v>
+        <v>46157.600659722222</v>
       </c>
       <c r="C44" s="2">
-        <v>46157.601377314801</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="L44" s="3" t="s">
+        <v>46157.601377314815</v>
+      </c>
+      <c r="D44" t="s">
+        <v>12</v>
+      </c>
+      <c r="F44" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" t="s">
+        <v>13</v>
+      </c>
+      <c r="H44" t="s">
+        <v>14</v>
+      </c>
+      <c r="I44" t="s">
+        <v>14</v>
+      </c>
+      <c r="J44" t="s">
+        <v>14</v>
+      </c>
+      <c r="K44" t="s">
+        <v>14</v>
+      </c>
+      <c r="L44" t="s">
         <v>51</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2">
+        <v>46157.68273148148</v>
+      </c>
+      <c r="C45" s="2">
+        <v>46157.683194444442</v>
+      </c>
+      <c r="D45" t="s">
+        <v>12</v>
+      </c>
+      <c r="F45" t="s">
+        <v>25</v>
+      </c>
+      <c r="G45" t="s">
+        <v>25</v>
+      </c>
+      <c r="H45" t="s">
+        <v>25</v>
+      </c>
+      <c r="I45" t="s">
+        <v>25</v>
+      </c>
+      <c r="J45" t="s">
+        <v>25</v>
+      </c>
+      <c r="K45" t="s">
+        <v>25</v>
+      </c>
+      <c r="L45" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2">
+        <v>46157.688738425924</v>
+      </c>
+      <c r="C46" s="2">
+        <v>46157.69</v>
+      </c>
+      <c r="D46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F46" t="s">
+        <v>18</v>
+      </c>
+      <c r="G46" t="s">
+        <v>14</v>
+      </c>
+      <c r="H46" t="s">
+        <v>14</v>
+      </c>
+      <c r="I46" t="s">
+        <v>14</v>
+      </c>
+      <c r="J46" t="s">
+        <v>14</v>
+      </c>
+      <c r="K46" t="s">
+        <v>14</v>
+      </c>
+      <c r="L46" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2">
+        <v>46157.690046296295</v>
+      </c>
+      <c r="C47" s="2">
+        <v>46157.691747685189</v>
+      </c>
+      <c r="D47" t="s">
+        <v>12</v>
+      </c>
+      <c r="F47" t="s">
+        <v>15</v>
+      </c>
+      <c r="G47" t="s">
+        <v>15</v>
+      </c>
+      <c r="H47" t="s">
+        <v>14</v>
+      </c>
+      <c r="I47" t="s">
+        <v>14</v>
+      </c>
+      <c r="J47" t="s">
+        <v>14</v>
+      </c>
+      <c r="K47" t="s">
+        <v>14</v>
+      </c>
+      <c r="L47" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2">
+        <v>46157.695231481484</v>
+      </c>
+      <c r="C48" s="2">
+        <v>46157.698738425926</v>
+      </c>
+      <c r="D48" t="s">
+        <v>12</v>
+      </c>
+      <c r="F48" t="s">
+        <v>15</v>
+      </c>
+      <c r="G48" t="s">
+        <v>15</v>
+      </c>
+      <c r="H48" t="s">
+        <v>15</v>
+      </c>
+      <c r="I48" t="s">
+        <v>15</v>
+      </c>
+      <c r="J48" t="s">
+        <v>15</v>
+      </c>
+      <c r="K48" t="s">
+        <v>15</v>
+      </c>
+      <c r="L48" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2">
+        <v>46160.363287037035</v>
+      </c>
+      <c r="C49" s="2">
+        <v>46160.365381944444</v>
+      </c>
+      <c r="D49" t="s">
+        <v>12</v>
+      </c>
+      <c r="F49" t="s">
+        <v>18</v>
+      </c>
+      <c r="G49" t="s">
+        <v>15</v>
+      </c>
+      <c r="H49" t="s">
+        <v>14</v>
+      </c>
+      <c r="I49" t="s">
+        <v>13</v>
+      </c>
+      <c r="J49" t="s">
+        <v>14</v>
+      </c>
+      <c r="K49" t="s">
+        <v>13</v>
+      </c>
+      <c r="L49" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2">
+        <v>46160.406956018516</v>
+      </c>
+      <c r="C50" s="2">
+        <v>46160.408622685187</v>
+      </c>
+      <c r="D50" t="s">
+        <v>12</v>
+      </c>
+      <c r="F50" t="s">
+        <v>18</v>
+      </c>
+      <c r="G50" t="s">
+        <v>14</v>
+      </c>
+      <c r="H50" t="s">
+        <v>13</v>
+      </c>
+      <c r="I50" t="s">
+        <v>14</v>
+      </c>
+      <c r="J50" t="s">
+        <v>13</v>
+      </c>
+      <c r="K50" t="s">
+        <v>13</v>
+      </c>
+      <c r="L50" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2">
+        <v>46160.423009259262</v>
+      </c>
+      <c r="C51" s="2">
+        <v>46160.424386574072</v>
+      </c>
+      <c r="D51" t="s">
+        <v>12</v>
+      </c>
+      <c r="F51" t="s">
+        <v>18</v>
+      </c>
+      <c r="G51" t="s">
+        <v>15</v>
+      </c>
+      <c r="H51" t="s">
+        <v>14</v>
+      </c>
+      <c r="I51" t="s">
+        <v>14</v>
+      </c>
+      <c r="J51" t="s">
+        <v>14</v>
+      </c>
+      <c r="K51" t="s">
+        <v>14</v>
+      </c>
+      <c r="L51" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2">
+        <v>46160.427858796298</v>
+      </c>
+      <c r="C52" s="2">
+        <v>46160.43037037037</v>
+      </c>
+      <c r="D52" t="s">
+        <v>12</v>
+      </c>
+      <c r="F52" t="s">
+        <v>18</v>
+      </c>
+      <c r="G52" t="s">
+        <v>13</v>
+      </c>
+      <c r="H52" t="s">
+        <v>13</v>
+      </c>
+      <c r="I52" t="s">
+        <v>13</v>
+      </c>
+      <c r="J52" t="s">
+        <v>13</v>
+      </c>
+      <c r="K52" t="s">
+        <v>13</v>
+      </c>
+      <c r="L52" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2">
+        <v>46160.457152777781</v>
+      </c>
+      <c r="C53" s="2">
+        <v>46160.460405092592</v>
+      </c>
+      <c r="D53" t="s">
+        <v>12</v>
+      </c>
+      <c r="F53" t="s">
+        <v>18</v>
+      </c>
+      <c r="G53" t="s">
+        <v>14</v>
+      </c>
+      <c r="H53" t="s">
+        <v>14</v>
+      </c>
+      <c r="I53" t="s">
+        <v>13</v>
+      </c>
+      <c r="J53" t="s">
+        <v>14</v>
+      </c>
+      <c r="K53" t="s">
+        <v>14</v>
+      </c>
+      <c r="L53" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2">
+        <v>46160.466053240743</v>
+      </c>
+      <c r="C54" s="2">
+        <v>46160.46733796296</v>
+      </c>
+      <c r="D54" t="s">
+        <v>12</v>
+      </c>
+      <c r="F54" t="s">
+        <v>13</v>
+      </c>
+      <c r="G54" t="s">
+        <v>13</v>
+      </c>
+      <c r="H54" t="s">
+        <v>13</v>
+      </c>
+      <c r="I54" t="s">
+        <v>13</v>
+      </c>
+      <c r="J54" t="s">
+        <v>13</v>
+      </c>
+      <c r="K54" t="s">
+        <v>13</v>
+      </c>
+      <c r="L54" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2">
+        <v>46160.465914351851</v>
+      </c>
+      <c r="C55" s="2">
+        <v>46160.469710648147</v>
+      </c>
+      <c r="D55" t="s">
+        <v>12</v>
+      </c>
+      <c r="F55" t="s">
+        <v>15</v>
+      </c>
+      <c r="G55" t="s">
+        <v>15</v>
+      </c>
+      <c r="H55" t="s">
+        <v>15</v>
+      </c>
+      <c r="I55" t="s">
+        <v>15</v>
+      </c>
+      <c r="J55" t="s">
+        <v>15</v>
+      </c>
+      <c r="K55" t="s">
+        <v>15</v>
+      </c>
+      <c r="L55" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2">
+        <v>46160.533043981479</v>
+      </c>
+      <c r="C56" s="2">
+        <v>46160.537881944445</v>
+      </c>
+      <c r="D56" t="s">
+        <v>12</v>
+      </c>
+      <c r="F56" t="s">
+        <v>18</v>
+      </c>
+      <c r="G56" t="s">
+        <v>14</v>
+      </c>
+      <c r="H56" t="s">
+        <v>15</v>
+      </c>
+      <c r="I56" t="s">
+        <v>14</v>
+      </c>
+      <c r="J56" t="s">
+        <v>14</v>
+      </c>
+      <c r="K56" t="s">
+        <v>14</v>
+      </c>
+      <c r="L56" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2">
+        <v>46160.581620370373</v>
+      </c>
+      <c r="C57" s="2">
+        <v>46160.585949074077</v>
+      </c>
+      <c r="D57" t="s">
+        <v>12</v>
+      </c>
+      <c r="F57" t="s">
+        <v>18</v>
+      </c>
+      <c r="G57" t="s">
+        <v>14</v>
+      </c>
+      <c r="H57" t="s">
+        <v>14</v>
+      </c>
+      <c r="I57" t="s">
+        <v>14</v>
+      </c>
+      <c r="J57" t="s">
+        <v>14</v>
+      </c>
+      <c r="K57" t="s">
+        <v>13</v>
+      </c>
+      <c r="L57" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2">
+        <v>46160.757361111115</v>
+      </c>
+      <c r="C58" s="2">
+        <v>46160.759016203701</v>
+      </c>
+      <c r="D58" t="s">
+        <v>12</v>
+      </c>
+      <c r="F58" t="s">
+        <v>13</v>
+      </c>
+      <c r="G58" t="s">
+        <v>13</v>
+      </c>
+      <c r="H58" t="s">
+        <v>14</v>
+      </c>
+      <c r="I58" t="s">
+        <v>13</v>
+      </c>
+      <c r="J58" t="s">
+        <v>13</v>
+      </c>
+      <c r="K58" t="s">
+        <v>13</v>
+      </c>
+      <c r="L58" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/dados/administrativos.xlsx
+++ b/dados/administrativos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30117"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F5B4F6E4-274C-4CCE-B108-210258843EFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3774FF00-971D-42E0-BC80-7AA2044F84EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="78">
   <si>
     <t>Id</t>
   </si>
@@ -249,6 +249,27 @@
   </si>
   <si>
     <t xml:space="preserve">No momento só parabenizar a instituição muito bom mesmo. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">tudo maravilhoso </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A convocação </t>
+  </si>
+  <si>
+    <t>A presença do marketing nas instituições em relação a atividade culturais e artísticas e principalmente sobre meio ambiente e sustentabilidade.</t>
+  </si>
+  <si>
+    <t>Tudo bom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mas união com os colegas </t>
+  </si>
+  <si>
+    <t>Mais atividades relacionadas à diversidade cultural e étnica</t>
+  </si>
+  <si>
+    <t>Okokokok</t>
   </si>
 </sst>
 </file>
@@ -337,8 +358,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:L58" totalsRowShown="0">
-  <autoFilter ref="A1:L58" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:L65" totalsRowShown="0">
+  <autoFilter ref="A1:L65" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="9">
       <extLst>
@@ -428,7 +449,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="rt8JIBHfx0mATf2o1c2YZSr5bAZAsa1Hi1pL7TTHnqJUNzZHRkpMSUdPQTlTUEo3NEJCVk1XVTJGQy4u" isFormConnected="1" maxResponseId="57" latestEventMarker="24">
+      <xlmsforms:msForm id="rt8JIBHfx0mATf2o1c2YZSr5bAZAsa1Hi1pL7TTHnqJUNzZHRkpMSUdPQTlTUEo3NEJCVk1XVTJGQy4u" isFormConnected="1" maxResponseId="64" latestEventMarker="31">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -744,7 +765,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L58"/>
+  <dimension ref="A1:L65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="12" width="20" bestFit="1" customWidth="1"/>
@@ -2783,6 +2804,251 @@
         <v>70</v>
       </c>
     </row>
+    <row r="59" spans="1:12">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2">
+        <v>46160.820567129631</v>
+      </c>
+      <c r="C59" s="2">
+        <v>46160.822962962964</v>
+      </c>
+      <c r="D59" t="s">
+        <v>12</v>
+      </c>
+      <c r="F59" t="s">
+        <v>13</v>
+      </c>
+      <c r="G59" t="s">
+        <v>14</v>
+      </c>
+      <c r="H59" t="s">
+        <v>14</v>
+      </c>
+      <c r="I59" t="s">
+        <v>14</v>
+      </c>
+      <c r="J59" t="s">
+        <v>13</v>
+      </c>
+      <c r="K59" t="s">
+        <v>13</v>
+      </c>
+      <c r="L59" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2">
+        <v>46161.410219907404</v>
+      </c>
+      <c r="C60" s="2">
+        <v>46161.411574074074</v>
+      </c>
+      <c r="D60" t="s">
+        <v>12</v>
+      </c>
+      <c r="F60" t="s">
+        <v>18</v>
+      </c>
+      <c r="G60" t="s">
+        <v>13</v>
+      </c>
+      <c r="H60" t="s">
+        <v>14</v>
+      </c>
+      <c r="I60" t="s">
+        <v>14</v>
+      </c>
+      <c r="J60" t="s">
+        <v>14</v>
+      </c>
+      <c r="K60" t="s">
+        <v>13</v>
+      </c>
+      <c r="L60" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2">
+        <v>46161.445185185185</v>
+      </c>
+      <c r="C61" s="2">
+        <v>46161.448194444441</v>
+      </c>
+      <c r="D61" t="s">
+        <v>12</v>
+      </c>
+      <c r="F61" t="s">
+        <v>13</v>
+      </c>
+      <c r="G61" t="s">
+        <v>13</v>
+      </c>
+      <c r="H61" t="s">
+        <v>15</v>
+      </c>
+      <c r="I61" t="s">
+        <v>15</v>
+      </c>
+      <c r="J61" t="s">
+        <v>15</v>
+      </c>
+      <c r="K61" t="s">
+        <v>14</v>
+      </c>
+      <c r="L61" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2">
+        <v>46161.457060185188</v>
+      </c>
+      <c r="C62" s="2">
+        <v>46161.458043981482</v>
+      </c>
+      <c r="D62" t="s">
+        <v>12</v>
+      </c>
+      <c r="F62" t="s">
+        <v>18</v>
+      </c>
+      <c r="G62" t="s">
+        <v>15</v>
+      </c>
+      <c r="H62" t="s">
+        <v>14</v>
+      </c>
+      <c r="I62" t="s">
+        <v>14</v>
+      </c>
+      <c r="J62" t="s">
+        <v>14</v>
+      </c>
+      <c r="K62" t="s">
+        <v>14</v>
+      </c>
+      <c r="L62" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2">
+        <v>46161.586273148147</v>
+      </c>
+      <c r="C63" s="2">
+        <v>46161.589687500003</v>
+      </c>
+      <c r="D63" t="s">
+        <v>12</v>
+      </c>
+      <c r="F63" t="s">
+        <v>13</v>
+      </c>
+      <c r="G63" t="s">
+        <v>13</v>
+      </c>
+      <c r="H63" t="s">
+        <v>13</v>
+      </c>
+      <c r="I63" t="s">
+        <v>13</v>
+      </c>
+      <c r="J63" t="s">
+        <v>13</v>
+      </c>
+      <c r="K63" t="s">
+        <v>13</v>
+      </c>
+      <c r="L63" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2">
+        <v>46161.846909722219</v>
+      </c>
+      <c r="C64" s="2">
+        <v>46161.847974537035</v>
+      </c>
+      <c r="D64" t="s">
+        <v>12</v>
+      </c>
+      <c r="F64" t="s">
+        <v>13</v>
+      </c>
+      <c r="G64" t="s">
+        <v>13</v>
+      </c>
+      <c r="H64" t="s">
+        <v>14</v>
+      </c>
+      <c r="I64" t="s">
+        <v>14</v>
+      </c>
+      <c r="J64" t="s">
+        <v>13</v>
+      </c>
+      <c r="K64" t="s">
+        <v>13</v>
+      </c>
+      <c r="L64" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2">
+        <v>46163.269560185188</v>
+      </c>
+      <c r="C65" s="2">
+        <v>46163.270879629628</v>
+      </c>
+      <c r="D65" t="s">
+        <v>12</v>
+      </c>
+      <c r="F65" t="s">
+        <v>18</v>
+      </c>
+      <c r="G65" t="s">
+        <v>15</v>
+      </c>
+      <c r="H65" t="s">
+        <v>15</v>
+      </c>
+      <c r="I65" t="s">
+        <v>15</v>
+      </c>
+      <c r="J65" t="s">
+        <v>15</v>
+      </c>
+      <c r="K65" t="s">
+        <v>15</v>
+      </c>
+      <c r="L65" t="s">
+        <v>77</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/dados/administrativos.xlsx
+++ b/dados/administrativos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30117"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30110"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3774FF00-971D-42E0-BC80-7AA2044F84EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{29DB2C34-2E80-4E96-B755-E61079B36243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="87">
   <si>
     <t>Id</t>
   </si>
@@ -270,6 +270,33 @@
   </si>
   <si>
     <t>Okokokok</t>
+  </si>
+  <si>
+    <t>Muito bom.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sem sugestões </t>
+  </si>
+  <si>
+    <t>REGULAR</t>
+  </si>
+  <si>
+    <t>sem comentários no momento.</t>
+  </si>
+  <si>
+    <t>Mais atividades culturais e de meio ambiente</t>
+  </si>
+  <si>
+    <t>Percebe-se esforço institucional na implementação de melhorias, porém acredito que o feedback sobre os resultados da avaliação ainda pode ser mais claro, frequente e acessível aos colaboradores.</t>
+  </si>
+  <si>
+    <t>Parabenizar o padrão de excelência, e evoluir constantemente com novas parcerias.</t>
+  </si>
+  <si>
+    <t>no geral, a instituição cumpre com a sua missão</t>
+  </si>
+  <si>
+    <t>Sugiro melhorar a comunicação entre os setores e os alunos, especialmente em relação a prazos e orientações acadêmicas</t>
   </si>
 </sst>
 </file>
@@ -358,8 +385,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:L65" totalsRowShown="0">
-  <autoFilter ref="A1:L65" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:L75" totalsRowShown="0">
+  <autoFilter ref="A1:L75" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="9">
       <extLst>
@@ -449,7 +476,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="rt8JIBHfx0mATf2o1c2YZSr5bAZAsa1Hi1pL7TTHnqJUNzZHRkpMSUdPQTlTUEo3NEJCVk1XVTJGQy4u" isFormConnected="1" maxResponseId="64" latestEventMarker="31">
+      <xlmsforms:msForm id="rt8JIBHfx0mATf2o1c2YZSr5bAZAsa1Hi1pL7TTHnqJUNzZHRkpMSUdPQTlTUEo3NEJCVk1XVTJGQy4u" isFormConnected="1" maxResponseId="74" latestEventMarker="41">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -765,7 +792,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L65"/>
+  <dimension ref="A1:L75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="12" width="20" bestFit="1" customWidth="1"/>
@@ -3049,6 +3076,356 @@
         <v>77</v>
       </c>
     </row>
+    <row r="66" spans="1:12">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2">
+        <v>46163.432453703703</v>
+      </c>
+      <c r="C66" s="2">
+        <v>46163.432962962965</v>
+      </c>
+      <c r="D66" t="s">
+        <v>12</v>
+      </c>
+      <c r="F66" t="s">
+        <v>18</v>
+      </c>
+      <c r="G66" t="s">
+        <v>14</v>
+      </c>
+      <c r="H66" t="s">
+        <v>14</v>
+      </c>
+      <c r="I66" t="s">
+        <v>14</v>
+      </c>
+      <c r="J66" t="s">
+        <v>14</v>
+      </c>
+      <c r="K66" t="s">
+        <v>14</v>
+      </c>
+      <c r="L66" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2">
+        <v>46163.450613425928</v>
+      </c>
+      <c r="C67" s="2">
+        <v>46163.451331018521</v>
+      </c>
+      <c r="D67" t="s">
+        <v>12</v>
+      </c>
+      <c r="F67" t="s">
+        <v>18</v>
+      </c>
+      <c r="G67" t="s">
+        <v>14</v>
+      </c>
+      <c r="H67" t="s">
+        <v>14</v>
+      </c>
+      <c r="I67" t="s">
+        <v>14</v>
+      </c>
+      <c r="J67" t="s">
+        <v>14</v>
+      </c>
+      <c r="K67" t="s">
+        <v>14</v>
+      </c>
+      <c r="L67" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2">
+        <v>46163.445439814815</v>
+      </c>
+      <c r="C68" s="2">
+        <v>46163.452928240738</v>
+      </c>
+      <c r="D68" t="s">
+        <v>12</v>
+      </c>
+      <c r="F68" t="s">
+        <v>15</v>
+      </c>
+      <c r="G68" t="s">
+        <v>15</v>
+      </c>
+      <c r="H68" t="s">
+        <v>15</v>
+      </c>
+      <c r="I68" t="s">
+        <v>15</v>
+      </c>
+      <c r="J68" t="s">
+        <v>15</v>
+      </c>
+      <c r="K68" t="s">
+        <v>15</v>
+      </c>
+      <c r="L68" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2">
+        <v>46163.452546296299</v>
+      </c>
+      <c r="C69" s="2">
+        <v>46163.453518518516</v>
+      </c>
+      <c r="D69" t="s">
+        <v>12</v>
+      </c>
+      <c r="F69" t="s">
+        <v>18</v>
+      </c>
+      <c r="G69" t="s">
+        <v>14</v>
+      </c>
+      <c r="H69" t="s">
+        <v>14</v>
+      </c>
+      <c r="I69" t="s">
+        <v>14</v>
+      </c>
+      <c r="J69" t="s">
+        <v>14</v>
+      </c>
+      <c r="K69" t="s">
+        <v>14</v>
+      </c>
+      <c r="L69" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2">
+        <v>46163.459421296298</v>
+      </c>
+      <c r="C70" s="2">
+        <v>46163.45988425926</v>
+      </c>
+      <c r="D70" t="s">
+        <v>12</v>
+      </c>
+      <c r="F70" t="s">
+        <v>18</v>
+      </c>
+      <c r="G70" t="s">
+        <v>14</v>
+      </c>
+      <c r="H70" t="s">
+        <v>15</v>
+      </c>
+      <c r="I70" t="s">
+        <v>15</v>
+      </c>
+      <c r="J70" t="s">
+        <v>15</v>
+      </c>
+      <c r="K70" t="s">
+        <v>15</v>
+      </c>
+      <c r="L70" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2">
+        <v>46163.45857638889</v>
+      </c>
+      <c r="C71" s="2">
+        <v>46163.460324074076</v>
+      </c>
+      <c r="D71" t="s">
+        <v>12</v>
+      </c>
+      <c r="F71" t="s">
+        <v>18</v>
+      </c>
+      <c r="G71" t="s">
+        <v>14</v>
+      </c>
+      <c r="H71" t="s">
+        <v>15</v>
+      </c>
+      <c r="I71" t="s">
+        <v>15</v>
+      </c>
+      <c r="J71" t="s">
+        <v>15</v>
+      </c>
+      <c r="K71" t="s">
+        <v>14</v>
+      </c>
+      <c r="L71" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2">
+        <v>46163.458738425928</v>
+      </c>
+      <c r="C72" s="2">
+        <v>46163.462013888886</v>
+      </c>
+      <c r="D72" t="s">
+        <v>12</v>
+      </c>
+      <c r="F72" t="s">
+        <v>15</v>
+      </c>
+      <c r="G72" t="s">
+        <v>15</v>
+      </c>
+      <c r="H72" t="s">
+        <v>14</v>
+      </c>
+      <c r="I72" t="s">
+        <v>14</v>
+      </c>
+      <c r="J72" t="s">
+        <v>14</v>
+      </c>
+      <c r="K72" t="s">
+        <v>13</v>
+      </c>
+      <c r="L72" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2">
+        <v>46163.458796296298</v>
+      </c>
+      <c r="C73" s="2">
+        <v>46163.462465277778</v>
+      </c>
+      <c r="D73" t="s">
+        <v>12</v>
+      </c>
+      <c r="F73" t="s">
+        <v>13</v>
+      </c>
+      <c r="G73" t="s">
+        <v>13</v>
+      </c>
+      <c r="H73" t="s">
+        <v>13</v>
+      </c>
+      <c r="I73" t="s">
+        <v>13</v>
+      </c>
+      <c r="J73" t="s">
+        <v>13</v>
+      </c>
+      <c r="K73" t="s">
+        <v>13</v>
+      </c>
+      <c r="L73" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2">
+        <v>46163.581875000003</v>
+      </c>
+      <c r="C74" s="2">
+        <v>46163.582627314812</v>
+      </c>
+      <c r="D74" t="s">
+        <v>12</v>
+      </c>
+      <c r="F74" t="s">
+        <v>13</v>
+      </c>
+      <c r="G74" t="s">
+        <v>13</v>
+      </c>
+      <c r="H74" t="s">
+        <v>13</v>
+      </c>
+      <c r="I74" t="s">
+        <v>13</v>
+      </c>
+      <c r="J74" t="s">
+        <v>15</v>
+      </c>
+      <c r="K74" t="s">
+        <v>15</v>
+      </c>
+      <c r="L74" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" s="2">
+        <v>46163.606932870367</v>
+      </c>
+      <c r="C75" s="2">
+        <v>46163.609918981485</v>
+      </c>
+      <c r="D75" t="s">
+        <v>12</v>
+      </c>
+      <c r="F75" t="s">
+        <v>15</v>
+      </c>
+      <c r="G75" t="s">
+        <v>15</v>
+      </c>
+      <c r="H75" t="s">
+        <v>14</v>
+      </c>
+      <c r="I75" t="s">
+        <v>14</v>
+      </c>
+      <c r="J75" t="s">
+        <v>14</v>
+      </c>
+      <c r="K75" t="s">
+        <v>14</v>
+      </c>
+      <c r="L75" t="s">
+        <v>86</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/dados/administrativos.xlsx
+++ b/dados/administrativos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30121"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{29DB2C34-2E80-4E96-B755-E61079B36243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F5461343-80CD-428B-918E-56FDB1594264}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="91">
   <si>
     <t>Id</t>
   </si>
@@ -297,6 +297,18 @@
   </si>
   <si>
     <t>Sugiro melhorar a comunicação entre os setores e os alunos, especialmente em relação a prazos e orientações acadêmicas</t>
+  </si>
+  <si>
+    <t>Sem sugestão.</t>
+  </si>
+  <si>
+    <t>Como sugestão de melhoria, acredito que uma comunicação mais alinhada entre os setores e treinamentos periódicos podem contribuir para otimizar os processos e o atendimento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preciso de mais tempo para oferecer sugestões ou melhoria </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estou iniciando agora na instituição ainda não tive oportunidade de criar uma opinião sobre , mas acho interessante ter palestra e projetos relacionados sobre cultura e diversidade </t>
   </si>
 </sst>
 </file>
@@ -385,8 +397,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:L75" totalsRowShown="0">
-  <autoFilter ref="A1:L75" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:L80" totalsRowShown="0">
+  <autoFilter ref="A1:L80" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="9">
       <extLst>
@@ -476,7 +488,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="rt8JIBHfx0mATf2o1c2YZSr5bAZAsa1Hi1pL7TTHnqJUNzZHRkpMSUdPQTlTUEo3NEJCVk1XVTJGQy4u" isFormConnected="1" maxResponseId="74" latestEventMarker="41">
+      <xlmsforms:msForm id="rt8JIBHfx0mATf2o1c2YZSr5bAZAsa1Hi1pL7TTHnqJUNzZHRkpMSUdPQTlTUEo3NEJCVk1XVTJGQy4u" isFormConnected="1" maxResponseId="79" latestEventMarker="46">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -792,7 +804,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L75"/>
+  <dimension ref="A1:L80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="12" width="20" bestFit="1" customWidth="1"/>
@@ -3426,6 +3438,181 @@
         <v>86</v>
       </c>
     </row>
+    <row r="76" spans="1:12">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" s="2">
+        <v>46163.642835648148</v>
+      </c>
+      <c r="C76" s="2">
+        <v>46163.64329861111</v>
+      </c>
+      <c r="D76" t="s">
+        <v>12</v>
+      </c>
+      <c r="F76" t="s">
+        <v>18</v>
+      </c>
+      <c r="G76" t="s">
+        <v>14</v>
+      </c>
+      <c r="H76" t="s">
+        <v>15</v>
+      </c>
+      <c r="I76" t="s">
+        <v>15</v>
+      </c>
+      <c r="J76" t="s">
+        <v>14</v>
+      </c>
+      <c r="K76" t="s">
+        <v>14</v>
+      </c>
+      <c r="L76" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" s="2">
+        <v>46163.641087962962</v>
+      </c>
+      <c r="C77" s="2">
+        <v>46163.657951388886</v>
+      </c>
+      <c r="D77" t="s">
+        <v>12</v>
+      </c>
+      <c r="F77" t="s">
+        <v>15</v>
+      </c>
+      <c r="G77" t="s">
+        <v>15</v>
+      </c>
+      <c r="H77" t="s">
+        <v>15</v>
+      </c>
+      <c r="I77" t="s">
+        <v>15</v>
+      </c>
+      <c r="J77" t="s">
+        <v>15</v>
+      </c>
+      <c r="K77" t="s">
+        <v>15</v>
+      </c>
+      <c r="L77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" s="2">
+        <v>46164.487002314818</v>
+      </c>
+      <c r="C78" s="2">
+        <v>46164.487615740742</v>
+      </c>
+      <c r="D78" t="s">
+        <v>12</v>
+      </c>
+      <c r="F78" t="s">
+        <v>18</v>
+      </c>
+      <c r="G78" t="s">
+        <v>14</v>
+      </c>
+      <c r="H78" t="s">
+        <v>13</v>
+      </c>
+      <c r="I78" t="s">
+        <v>15</v>
+      </c>
+      <c r="J78" t="s">
+        <v>14</v>
+      </c>
+      <c r="K78" t="s">
+        <v>13</v>
+      </c>
+      <c r="L78" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" s="2">
+        <v>46164.635844907411</v>
+      </c>
+      <c r="C79" s="2">
+        <v>46164.636203703703</v>
+      </c>
+      <c r="D79" t="s">
+        <v>12</v>
+      </c>
+      <c r="F79" t="s">
+        <v>15</v>
+      </c>
+      <c r="G79" t="s">
+        <v>15</v>
+      </c>
+      <c r="H79" t="s">
+        <v>15</v>
+      </c>
+      <c r="I79" t="s">
+        <v>15</v>
+      </c>
+      <c r="J79" t="s">
+        <v>13</v>
+      </c>
+      <c r="K79" t="s">
+        <v>14</v>
+      </c>
+      <c r="L79" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" s="2">
+        <v>46164.724583333336</v>
+      </c>
+      <c r="C80" s="2">
+        <v>46164.725717592592</v>
+      </c>
+      <c r="D80" t="s">
+        <v>12</v>
+      </c>
+      <c r="F80" t="s">
+        <v>13</v>
+      </c>
+      <c r="G80" t="s">
+        <v>14</v>
+      </c>
+      <c r="H80" t="s">
+        <v>14</v>
+      </c>
+      <c r="I80" t="s">
+        <v>14</v>
+      </c>
+      <c r="J80" t="s">
+        <v>14</v>
+      </c>
+      <c r="K80" t="s">
+        <v>15</v>
+      </c>
+      <c r="L80" t="s">
+        <v>90</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/dados/administrativos.xlsx
+++ b/dados/administrativos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30121"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30117"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F5461343-80CD-428B-918E-56FDB1594264}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D3CA29C-5687-43AB-B374-FD09B9F3D857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="92">
   <si>
     <t>Id</t>
   </si>
@@ -309,6 +309,9 @@
   </si>
   <si>
     <t xml:space="preserve">Estou iniciando agora na instituição ainda não tive oportunidade de criar uma opinião sobre , mas acho interessante ter palestra e projetos relacionados sobre cultura e diversidade </t>
+  </si>
+  <si>
+    <t>Apesar de trabalhos em grupo estimularem algumas habilidades importantes e simularem um ambiente corporativo, gostaria de mais trabalhos individuais.</t>
   </si>
 </sst>
 </file>
@@ -397,8 +400,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:L80" totalsRowShown="0">
-  <autoFilter ref="A1:L80" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:L81" totalsRowShown="0">
+  <autoFilter ref="A1:L81" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="9">
       <extLst>
@@ -488,7 +491,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="rt8JIBHfx0mATf2o1c2YZSr5bAZAsa1Hi1pL7TTHnqJUNzZHRkpMSUdPQTlTUEo3NEJCVk1XVTJGQy4u" isFormConnected="1" maxResponseId="79" latestEventMarker="46">
+      <xlmsforms:msForm id="rt8JIBHfx0mATf2o1c2YZSr5bAZAsa1Hi1pL7TTHnqJUNzZHRkpMSUdPQTlTUEo3NEJCVk1XVTJGQy4u" isFormConnected="1" maxResponseId="80" latestEventMarker="47">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -804,7 +807,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L80"/>
+  <dimension ref="A1:L81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="12" width="20" bestFit="1" customWidth="1"/>
@@ -3613,6 +3616,41 @@
         <v>90</v>
       </c>
     </row>
+    <row r="81" spans="1:12">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" s="2">
+        <v>46167.363136574073</v>
+      </c>
+      <c r="C81" s="2">
+        <v>46167.364374999997</v>
+      </c>
+      <c r="D81" t="s">
+        <v>12</v>
+      </c>
+      <c r="F81" t="s">
+        <v>18</v>
+      </c>
+      <c r="G81" t="s">
+        <v>13</v>
+      </c>
+      <c r="H81" t="s">
+        <v>14</v>
+      </c>
+      <c r="I81" t="s">
+        <v>15</v>
+      </c>
+      <c r="J81" t="s">
+        <v>14</v>
+      </c>
+      <c r="K81" t="s">
+        <v>14</v>
+      </c>
+      <c r="L81" t="s">
+        <v>91</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/dados/administrativos.xlsx
+++ b/dados/administrativos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D3CA29C-5687-43AB-B374-FD09B9F3D857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3125DA67-9FE2-4DDE-A454-BD7A8599BCE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="94">
   <si>
     <t>Id</t>
   </si>
@@ -312,6 +312,12 @@
   </si>
   <si>
     <t>Apesar de trabalhos em grupo estimularem algumas habilidades importantes e simularem um ambiente corporativo, gostaria de mais trabalhos individuais.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gostaria que   a empresa  reveste a questão da  escala do  sábado. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suporte pedagogico para novos funcionarios, programas sanidade mental e convivio coletivo. </t>
   </si>
 </sst>
 </file>
@@ -400,8 +406,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:L81" totalsRowShown="0">
-  <autoFilter ref="A1:L81" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:L83" totalsRowShown="0">
+  <autoFilter ref="A1:L83" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="9">
       <extLst>
@@ -491,7 +497,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="rt8JIBHfx0mATf2o1c2YZSr5bAZAsa1Hi1pL7TTHnqJUNzZHRkpMSUdPQTlTUEo3NEJCVk1XVTJGQy4u" isFormConnected="1" maxResponseId="80" latestEventMarker="47">
+      <xlmsforms:msForm id="rt8JIBHfx0mATf2o1c2YZSr5bAZAsa1Hi1pL7TTHnqJUNzZHRkpMSUdPQTlTUEo3NEJCVk1XVTJGQy4u" isFormConnected="1" maxResponseId="82" latestEventMarker="49">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -807,7 +813,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L81"/>
+  <dimension ref="A1:L83"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="12" width="20" bestFit="1" customWidth="1"/>
@@ -3651,6 +3657,76 @@
         <v>91</v>
       </c>
     </row>
+    <row r="82" spans="1:12">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2">
+        <v>46167.569837962961</v>
+      </c>
+      <c r="C82" s="2">
+        <v>46167.573993055557</v>
+      </c>
+      <c r="D82" t="s">
+        <v>12</v>
+      </c>
+      <c r="F82" t="s">
+        <v>15</v>
+      </c>
+      <c r="G82" t="s">
+        <v>15</v>
+      </c>
+      <c r="H82" t="s">
+        <v>15</v>
+      </c>
+      <c r="I82" t="s">
+        <v>15</v>
+      </c>
+      <c r="J82" t="s">
+        <v>21</v>
+      </c>
+      <c r="K82" t="s">
+        <v>15</v>
+      </c>
+      <c r="L82" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" s="2">
+        <v>46167.64371527778</v>
+      </c>
+      <c r="C83" s="2">
+        <v>46167.645104166666</v>
+      </c>
+      <c r="D83" t="s">
+        <v>12</v>
+      </c>
+      <c r="F83" t="s">
+        <v>18</v>
+      </c>
+      <c r="G83" t="s">
+        <v>14</v>
+      </c>
+      <c r="H83" t="s">
+        <v>15</v>
+      </c>
+      <c r="I83" t="s">
+        <v>15</v>
+      </c>
+      <c r="J83" t="s">
+        <v>15</v>
+      </c>
+      <c r="K83" t="s">
+        <v>15</v>
+      </c>
+      <c r="L83" t="s">
+        <v>93</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/dados/administrativos.xlsx
+++ b/dados/administrativos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30117"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30125"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3125DA67-9FE2-4DDE-A454-BD7A8599BCE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1039A154-7473-4F45-8DA2-A48CD4F4DB30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="94">
   <si>
     <t>Id</t>
   </si>
@@ -406,8 +406,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:L83" totalsRowShown="0">
-  <autoFilter ref="A1:L83" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:L84" totalsRowShown="0">
+  <autoFilter ref="A1:L84" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="9">
       <extLst>
@@ -497,7 +497,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="rt8JIBHfx0mATf2o1c2YZSr5bAZAsa1Hi1pL7TTHnqJUNzZHRkpMSUdPQTlTUEo3NEJCVk1XVTJGQy4u" isFormConnected="1" maxResponseId="82" latestEventMarker="49">
+      <xlmsforms:msForm id="rt8JIBHfx0mATf2o1c2YZSr5bAZAsa1Hi1pL7TTHnqJUNzZHRkpMSUdPQTlTUEo3NEJCVk1XVTJGQy4u" isFormConnected="1" maxResponseId="83" latestEventMarker="50">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -813,7 +813,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L83"/>
+  <dimension ref="A1:L84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="12" width="20" bestFit="1" customWidth="1"/>
@@ -3727,6 +3727,41 @@
         <v>93</v>
       </c>
     </row>
+    <row r="84" spans="1:12">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" s="2">
+        <v>46169.517256944448</v>
+      </c>
+      <c r="C84" s="2">
+        <v>46169.517812500002</v>
+      </c>
+      <c r="D84" t="s">
+        <v>12</v>
+      </c>
+      <c r="F84" t="s">
+        <v>15</v>
+      </c>
+      <c r="G84" t="s">
+        <v>15</v>
+      </c>
+      <c r="H84" t="s">
+        <v>15</v>
+      </c>
+      <c r="I84" t="s">
+        <v>15</v>
+      </c>
+      <c r="J84" t="s">
+        <v>15</v>
+      </c>
+      <c r="K84" t="s">
+        <v>15</v>
+      </c>
+      <c r="L84" t="s">
+        <v>79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/dados/administrativos.xlsx
+++ b/dados/administrativos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1039A154-7473-4F45-8DA2-A48CD4F4DB30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{904C0876-8953-4116-8656-8E2B53AFBA7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="97">
   <si>
     <t>Id</t>
   </si>
@@ -318,6 +318,15 @@
   </si>
   <si>
     <t xml:space="preserve">Suporte pedagogico para novos funcionarios, programas sanidade mental e convivio coletivo. </t>
+  </si>
+  <si>
+    <t>No momento, sem sugestões!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não tenho sugestões </t>
+  </si>
+  <si>
+    <t>Incentivar mais e cultura e arte na IES.</t>
   </si>
 </sst>
 </file>
@@ -406,8 +415,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:L84" totalsRowShown="0">
-  <autoFilter ref="A1:L84" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:L88" totalsRowShown="0">
+  <autoFilter ref="A1:L88" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="9">
       <extLst>
@@ -497,7 +506,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="rt8JIBHfx0mATf2o1c2YZSr5bAZAsa1Hi1pL7TTHnqJUNzZHRkpMSUdPQTlTUEo3NEJCVk1XVTJGQy4u" isFormConnected="1" maxResponseId="83" latestEventMarker="50">
+      <xlmsforms:msForm id="rt8JIBHfx0mATf2o1c2YZSr5bAZAsa1Hi1pL7TTHnqJUNzZHRkpMSUdPQTlTUEo3NEJCVk1XVTJGQy4u" isFormConnected="1" maxResponseId="87" latestEventMarker="54">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -813,7 +822,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L84"/>
+  <dimension ref="A1:L88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="12" width="20" bestFit="1" customWidth="1"/>
@@ -3762,6 +3771,146 @@
         <v>79</v>
       </c>
     </row>
+    <row r="85" spans="1:12">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" s="2">
+        <v>46171.44971064815</v>
+      </c>
+      <c r="C85" s="2">
+        <v>46171.453483796293</v>
+      </c>
+      <c r="D85" t="s">
+        <v>12</v>
+      </c>
+      <c r="F85" t="s">
+        <v>15</v>
+      </c>
+      <c r="G85" t="s">
+        <v>14</v>
+      </c>
+      <c r="H85" t="s">
+        <v>14</v>
+      </c>
+      <c r="I85" t="s">
+        <v>14</v>
+      </c>
+      <c r="J85" t="s">
+        <v>15</v>
+      </c>
+      <c r="K85" t="s">
+        <v>14</v>
+      </c>
+      <c r="L85" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" s="2">
+        <v>46171.46603009259</v>
+      </c>
+      <c r="C86" s="2">
+        <v>46171.466620370367</v>
+      </c>
+      <c r="D86" t="s">
+        <v>12</v>
+      </c>
+      <c r="F86" t="s">
+        <v>18</v>
+      </c>
+      <c r="G86" t="s">
+        <v>14</v>
+      </c>
+      <c r="H86" t="s">
+        <v>14</v>
+      </c>
+      <c r="I86" t="s">
+        <v>14</v>
+      </c>
+      <c r="J86" t="s">
+        <v>14</v>
+      </c>
+      <c r="K86" t="s">
+        <v>14</v>
+      </c>
+      <c r="L86" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" s="2">
+        <v>46171.473391203705</v>
+      </c>
+      <c r="C87" s="2">
+        <v>46171.473854166667</v>
+      </c>
+      <c r="D87" t="s">
+        <v>12</v>
+      </c>
+      <c r="F87" t="s">
+        <v>18</v>
+      </c>
+      <c r="G87" t="s">
+        <v>14</v>
+      </c>
+      <c r="H87" t="s">
+        <v>14</v>
+      </c>
+      <c r="I87" t="s">
+        <v>14</v>
+      </c>
+      <c r="J87" t="s">
+        <v>14</v>
+      </c>
+      <c r="K87" t="s">
+        <v>14</v>
+      </c>
+      <c r="L87" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" s="2">
+        <v>46171.509652777779</v>
+      </c>
+      <c r="C88" s="2">
+        <v>46171.510682870372</v>
+      </c>
+      <c r="D88" t="s">
+        <v>12</v>
+      </c>
+      <c r="F88" t="s">
+        <v>18</v>
+      </c>
+      <c r="G88" t="s">
+        <v>15</v>
+      </c>
+      <c r="H88" t="s">
+        <v>15</v>
+      </c>
+      <c r="I88" t="s">
+        <v>15</v>
+      </c>
+      <c r="J88" t="s">
+        <v>15</v>
+      </c>
+      <c r="K88" t="s">
+        <v>14</v>
+      </c>
+      <c r="L88" t="s">
+        <v>96</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
